--- a/测试环境/小表.xlsx
+++ b/测试环境/小表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9c4e8455bcdffc71/Desktop/发送到服务器的文件/excel小表并大表/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="11_AD4DA82427541F7ACA7EB8D5404B1EBE6AE8DE11" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D952E8B2-C067-4642-8C75-EA7B93C55053}"/>
+  <xr:revisionPtr revIDLastSave="31" documentId="11_AD4DA82427541F7ACA7EB8D5404B1EBE6AE8DE11" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EDCB04DA-1A1F-459E-944B-F82C46626DB5}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4290" yWindow="4290" windowWidth="38700" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NAME1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="10">
   <si>
     <t>A</t>
   </si>
@@ -61,9 +61,15 @@
   </si>
   <si>
     <t>1 1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">11 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>T</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -86,12 +92,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -106,8 +118,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -388,10 +402,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -416,8 +430,17 @@
       <c r="H1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>30</v>
       </c>
@@ -439,8 +462,14 @@
       <c r="H2">
         <v>33</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>45</v>
       </c>
@@ -465,8 +494,17 @@
       <c r="H3">
         <v>97</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -491,8 +529,14 @@
       <c r="H4">
         <v>64</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>74</v>
       </c>
@@ -517,8 +561,14 @@
       <c r="H5">
         <v>24</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="C6">
         <v>17</v>
       </c>
@@ -531,8 +581,11 @@
       <c r="H6">
         <v>39</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>54</v>
       </c>
@@ -548,8 +601,17 @@
       <c r="H7">
         <v>56</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>21</v>
       </c>
@@ -571,8 +633,11 @@
       <c r="H8">
         <v>96</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B9">
         <v>29</v>
       </c>
@@ -591,8 +656,14 @@
       <c r="H9">
         <v>2</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I9">
+        <v>1</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>24</v>
       </c>
@@ -608,8 +679,11 @@
       <c r="G10">
         <v>42</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>31</v>
       </c>
@@ -624,6 +698,12 @@
       </c>
       <c r="G11">
         <v>32</v>
+      </c>
+      <c r="I11">
+        <v>1</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -638,10 +718,10 @@
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1">
+      <c r="A1" s="1">
         <v>1</v>
       </c>
-      <c r="B1">
+      <c r="B1" s="1">
         <v>11</v>
       </c>
       <c r="C1">
@@ -653,10 +733,10 @@
       <c r="E1">
         <v>6</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H1">
